--- a/RR Equation Solver/Excel/RR_Huang.xlsx
+++ b/RR Equation Solver/Excel/RR_Huang.xlsx
@@ -5,22 +5,24 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\coe-fs.engr.tamu.edu\Staff\huangtj\Desktop\RR Equation Solver\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tamucs-my.sharepoint.com/personal/huangtj_tamu_edu/Documents/Postdoc/RR equation/Fianal Paper/Revision/RR Equation Solver/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1C4474-9123-4309-9D92-6551480FE3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D3E004C-DAFD-4BBC-96A1-EA026A6EA90B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" sheetId="2" r:id="rId2"/>
+    <sheet name="InitialGradient" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="29">
   <si>
     <t>RR_Huang One-Page Dynamic Template</t>
   </si>
@@ -43,13 +45,70 @@
     <t>K Value (NP-1, NC)</t>
   </si>
   <si>
-    <t>beta</t>
-  </si>
-  <si>
     <t>Initila Guess (NP-1)</t>
   </si>
   <si>
-    <t>Before Run: Alt + F11: File→import RR_Huang_Dynamic.bas</t>
+    <t>Solver</t>
+  </si>
+  <si>
+    <t>VBA</t>
+  </si>
+  <si>
+    <t>iterCount</t>
+  </si>
+  <si>
+    <t>ierr</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Converged.</t>
+  </si>
+  <si>
+    <t>Iteration</t>
+  </si>
+  <si>
+    <t>Residual</t>
+  </si>
+  <si>
+    <t>beta_1</t>
+  </si>
+  <si>
+    <t>beta_2</t>
+  </si>
+  <si>
+    <t>beta_3</t>
+  </si>
+  <si>
+    <t>beta solution</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Centroid computed successfully.</t>
+  </si>
+  <si>
+    <t>Centroid</t>
+  </si>
+  <si>
+    <t>Vertices</t>
+  </si>
+  <si>
+    <t>Vertex</t>
+  </si>
+  <si>
+    <t>grad_norm</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>Press 'Initial Guess' or Enter Manually</t>
+  </si>
+  <si>
+    <t>If Macro cannot be found,  press Alt + F11 to open VBA object and File→import *.bas</t>
   </si>
 </sst>
 </file>
@@ -59,7 +118,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000000000000000"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -103,13 +162,49 @@
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="12"/>
+      <color theme="3" tint="0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="3" tint="0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -151,6 +246,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -179,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -191,11 +298,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -206,13 +309,34 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -234,6 +358,14 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -247,7 +379,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>3</xdr:col>
-          <xdr:colOff>1543050</xdr:colOff>
+          <xdr:colOff>809625</xdr:colOff>
           <xdr:row>6</xdr:row>
           <xdr:rowOff>200025</xdr:rowOff>
         </xdr:to>
@@ -281,14 +413,14 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="45720" tIns="41148" rIns="45720" bIns="41148" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="36576" rIns="36576" bIns="36576" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
                 <a:defRPr sz="1000"/>
               </a:pPr>
               <a:r>
-                <a:rPr lang="en-US" sz="2000" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0">
                   <a:solidFill>
                     <a:srgbClr val="FF0000"/>
                   </a:solidFill>
@@ -306,7 +438,151 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>1133475</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>4</xdr:col>
+          <xdr:colOff>1876425</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>200025</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1026" name="Initial Guess" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1026"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="36576" rIns="36576" bIns="36576" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                  <a:ea typeface="Calibri"/>
+                  <a:cs typeface="Calibri"/>
+                </a:rPr>
+                <a:t>Initial Guess</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor>
+        <xdr:from>
+          <xdr:col>5</xdr:col>
+          <xdr:colOff>304800</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>9525</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>1047750</xdr:colOff>
+          <xdr:row>7</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="1027" name="Initial Guess" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1027"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="9525">
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="36576" tIns="36576" rIns="36576" bIns="36576" anchor="ctr" upright="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="1800" b="1" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri"/>
+                  <a:ea typeface="Calibri"/>
+                  <a:cs typeface="Calibri"/>
+                </a:rPr>
+                <a:t>Reset Result</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -462,27 +738,28 @@
   <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="27.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="8" width="26" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.625" style="8"/>
+    <col min="1" max="1" width="39.375" style="6" customWidth="1"/>
+    <col min="2" max="2" width="27.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.625" style="6" customWidth="1"/>
+    <col min="4" max="8" width="26" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="18.75">
-      <c r="A2" s="13" t="s">
-        <v>9</v>
+      <c r="A2" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -506,8 +783,8 @@
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="9">
-        <v>6</v>
+      <c r="B4" s="7">
+        <v>7</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -520,7 +797,7 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="7">
         <v>3</v>
       </c>
       <c r="C5" s="4"/>
@@ -534,7 +811,7 @@
       <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="8">
         <v>1E-8</v>
       </c>
       <c r="C6" s="4"/>
@@ -548,11 +825,11 @@
       <c r="A7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="7">
         <v>20</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
+      <c r="D7" s="19"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -578,29 +855,31 @@
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
-    <row r="10" spans="1:9" s="11" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="10" spans="1:9" s="9" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="2">
-        <v>0.18840263292639201</v>
+        <v>0.14281187032655501</v>
       </c>
       <c r="C10" s="2">
-        <v>9.2626724386011702E-2</v>
+        <v>0.27408215122531099</v>
       </c>
       <c r="D10" s="2">
-        <v>0.21838371001506901</v>
+        <v>0.162033782033395</v>
       </c>
       <c r="E10" s="2">
-        <v>0.138802268941497</v>
+        <v>0.109107773320094</v>
       </c>
       <c r="F10" s="2">
-        <v>0.249847073182628</v>
+        <v>0.16953002192526101</v>
       </c>
       <c r="G10" s="2">
-        <v>0.11193759054840299</v>
-      </c>
-      <c r="H10" s="2"/>
+        <v>7.4075635582188104E-3</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0.13502683761116599</v>
+      </c>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="1:9" ht="17.100000000000001" customHeight="1">
@@ -613,75 +892,82 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" spans="1:9" s="12" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="12" spans="1:9" s="10" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="3">
-        <v>0.98299773525365297</v>
+        <v>0.299562537946018</v>
       </c>
       <c r="C12" s="3">
-        <v>1.8561961514832299</v>
+        <v>0.68853296148854104</v>
       </c>
       <c r="D12" s="3">
-        <v>0.26549768272052598</v>
+        <v>0.76675902568926702</v>
       </c>
       <c r="E12" s="3">
-        <v>0.17998224513882999</v>
+        <v>6.9994579753463801</v>
       </c>
       <c r="F12" s="3">
-        <v>1.50301456518865</v>
+        <v>0.224124206329609</v>
       </c>
       <c r="G12" s="3">
-        <v>1.6418640825622099</v>
-      </c>
-      <c r="H12" s="3"/>
+        <v>8.8477385360543295</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.208901518404109</v>
+      </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9" s="12" customFormat="1" ht="17.100000000000001" customHeight="1">
+    <row r="13" spans="1:9" s="10" customFormat="1" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="3"/>
       <c r="B13" s="3">
-        <v>1.97978901328667</v>
+        <v>0.56181587719440196</v>
       </c>
       <c r="C13" s="3">
-        <v>0.41411923155191499</v>
+        <v>0.73533576716833604</v>
       </c>
       <c r="D13" s="3">
-        <v>1.4963161185761</v>
+        <v>0.55342331098196096</v>
       </c>
       <c r="E13" s="3">
-        <v>0.37405697639804902</v>
+        <v>7.2628642074918996</v>
       </c>
       <c r="F13" s="3">
-        <v>2.4162085933306798</v>
+        <v>1.3149587026313501</v>
       </c>
       <c r="G13" s="3">
-        <v>0.151659591934375</v>
-      </c>
-      <c r="H13" s="3"/>
+        <v>1.6493981742955</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.30222130733796998</v>
+      </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:9" s="12" customFormat="1" ht="18.75">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5">
-        <v>2.98326012998018</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0.11647840710729999</v>
-      </c>
-      <c r="D14" s="5">
-        <v>2.3868244189270902</v>
-      </c>
-      <c r="E14" s="5">
-        <v>0.15055515629276001</v>
-      </c>
-      <c r="F14" s="5">
-        <v>1.3005783074139401</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0.58813538114738795</v>
-      </c>
-      <c r="H14" s="5"/>
+    <row r="14" spans="1:9" s="10" customFormat="1" ht="17.100000000000001" customHeight="1">
+      <c r="A14" s="3"/>
+      <c r="B14" s="18">
+        <v>0.56164721184604705</v>
+      </c>
+      <c r="C14" s="18">
+        <v>1.0233176683490199</v>
+      </c>
+      <c r="D14" s="18">
+        <v>0.89969677923737401</v>
+      </c>
+      <c r="E14" s="18">
+        <v>5.1408004453284004</v>
+      </c>
+      <c r="F14" s="18">
+        <v>0.39248355856856498</v>
+      </c>
+      <c r="G14" s="18">
+        <v>1.8519909365212901</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.93197556218031496</v>
+      </c>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="18.75">
       <c r="A15" s="4"/>
@@ -693,61 +979,63 @@
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
     </row>
-    <row r="16" spans="1:9" s="17" customFormat="1" ht="18.75">
-      <c r="A16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="18" t="s">
+    <row r="16" spans="1:9" ht="18.75">
+      <c r="A16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-    </row>
-    <row r="17" spans="1:8" s="17" customFormat="1" ht="17.100000000000001" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="C17" s="18">
-        <v>4.6067332184713171E-2</v>
-      </c>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-    </row>
-    <row r="18" spans="1:8" s="17" customFormat="1" ht="18.75">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="C18" s="18">
-        <v>0.2547872317290017</v>
-      </c>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-    </row>
-    <row r="19" spans="1:8" s="17" customFormat="1" ht="18.75">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="C19" s="18">
-        <v>0.34178167939955451</v>
-      </c>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" spans="1:8" ht="17.100000000000001" customHeight="1">
+      <c r="A17" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0.22404262259360999</v>
+      </c>
+      <c r="C17" s="12">
+        <v>-0.1456806702306426</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+    <row r="18" spans="1:8" ht="18.75">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5">
+        <v>0.48532213967052285</v>
+      </c>
+      <c r="C18" s="12">
+        <v>0.23116073261876363</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+    </row>
+    <row r="19" spans="1:8" ht="18.75">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5">
+        <v>-0.29987422001748143</v>
+      </c>
+      <c r="C19" s="12">
+        <v>0.27310297609988493</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" ht="18.75">
       <c r="A20" s="4"/>
@@ -783,14 +1071,15 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x14">
       <controls>
         <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId3" name="Button 1">
+            <control shapeId="1025" r:id="rId4" name="Button 1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!RR_Huang_RunFromSheet">
                 <anchor moveWithCells="1">
                   <from>
@@ -801,9 +1090,53 @@
                   </from>
                   <to>
                     <xdr:col>3</xdr:col>
-                    <xdr:colOff>1543050</xdr:colOff>
+                    <xdr:colOff>809625</xdr:colOff>
                     <xdr:row>6</xdr:row>
                     <xdr:rowOff>200025</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1026" r:id="rId5" name="Initial Guess">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!InitialGradient_CreateSheet">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>3</xdr:col>
+                    <xdr:colOff>1133475</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>4</xdr:col>
+                    <xdr:colOff>1876425</xdr:colOff>
+                    <xdr:row>6</xdr:row>
+                    <xdr:rowOff>200025</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <control shapeId="1027" r:id="rId6" name="Initial Guess">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0" macro="[0]!RR_Huang_ResetResults">
+                <anchor moveWithCells="1" sizeWithCells="1">
+                  <from>
+                    <xdr:col>5</xdr:col>
+                    <xdr:colOff>304800</xdr:colOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>9525</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>6</xdr:col>
+                    <xdr:colOff>1047750</xdr:colOff>
+                    <xdr:row>7</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -814,4 +1147,393 @@
     </mc:Choice>
   </mc:AlternateContent>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FACFE3C-20E4-43FA-8628-E5322CF842B1}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="18.75" style="14" customWidth="1"/>
+    <col min="2" max="2" width="17.25" style="14" customWidth="1"/>
+    <col min="3" max="3" width="9" style="14"/>
+    <col min="4" max="4" width="15.125" style="14" customWidth="1"/>
+    <col min="5" max="5" width="23" style="14" customWidth="1"/>
+    <col min="6" max="6" width="13.125" style="14" customWidth="1"/>
+    <col min="7" max="7" width="16.75" style="14" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="13">
+        <v>6</v>
+      </c>
+      <c r="E2" s="17"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="13">
+        <v>0</v>
+      </c>
+      <c r="E3" s="17"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="17"/>
+    </row>
+    <row r="11" spans="1:7" s="15" customFormat="1">
+      <c r="A11" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="14">
+        <v>1</v>
+      </c>
+      <c r="B12" s="14">
+        <v>0.43469776401259119</v>
+      </c>
+      <c r="D12" s="14">
+        <v>1</v>
+      </c>
+      <c r="E12" s="14">
+        <v>0.22404262259360999</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0.48532213967052285</v>
+      </c>
+      <c r="G12" s="14">
+        <v>-0.29987422001748143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="14">
+        <v>2</v>
+      </c>
+      <c r="B13" s="14">
+        <v>0.17043103327802833</v>
+      </c>
+      <c r="D13" s="14">
+        <v>2</v>
+      </c>
+      <c r="E13" s="14">
+        <v>-0.15244652733275654</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0.65089924284562062</v>
+      </c>
+      <c r="G13" s="14">
+        <v>-4.6261618878331865E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="14">
+        <v>3</v>
+      </c>
+      <c r="B14" s="14">
+        <v>1.7462440348752481E-2</v>
+      </c>
+      <c r="D14" s="14">
+        <v>3</v>
+      </c>
+      <c r="E14" s="14">
+        <v>-0.13518678741716611</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0.26841646405445607</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0.16255413285814699</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="14">
+        <v>4</v>
+      </c>
+      <c r="B15" s="14">
+        <v>1.0507380081777916E-3</v>
+      </c>
+      <c r="D15" s="14">
+        <v>4</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-0.14578032333809926</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0.22839280110389068</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0.27597701107204409</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="14">
+        <v>5</v>
+      </c>
+      <c r="B16" s="14">
+        <v>1.0709162244375346E-6</v>
+      </c>
+      <c r="D16" s="14">
+        <v>5</v>
+      </c>
+      <c r="E16" s="14">
+        <v>-0.14568061403611898</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0.23115791171995476</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0.27310545152481419</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="14">
+        <v>6</v>
+      </c>
+      <c r="B17" s="14">
+        <v>2.5948667788599188E-12</v>
+      </c>
+      <c r="D17" s="14">
+        <v>6</v>
+      </c>
+      <c r="E17" s="14">
+        <v>-0.1456806702306426</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0.23116073261876363</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0.27310297609988493</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48FC9CCB-9961-4465-A2EC-830E69121B2F}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="21.75" defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="16384" width="21.75" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="23" customFormat="1">
+      <c r="A3" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="B4" s="20">
+        <v>0.22404262259360999</v>
+      </c>
+      <c r="C4" s="20">
+        <v>0.48532213967052285</v>
+      </c>
+      <c r="D4" s="20">
+        <v>-0.29987422001748143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="22" customFormat="1">
+      <c r="A7" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="20">
+        <v>1</v>
+      </c>
+      <c r="B8" s="20">
+        <v>-0.37756784999999998</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0.52768972999999997</v>
+      </c>
+      <c r="D8" s="20">
+        <v>1.9968099399999999</v>
+      </c>
+      <c r="E8" s="20">
+        <v>1.0421279733729811</v>
+      </c>
+      <c r="F8" s="20">
+        <v>0.15141853818474901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="20">
+        <v>2</v>
+      </c>
+      <c r="B9" s="20">
+        <v>0.79581816000000005</v>
+      </c>
+      <c r="C9" s="20">
+        <v>0.27975813999999999</v>
+      </c>
+      <c r="D9" s="20">
+        <v>0.36970993000000002</v>
+      </c>
+      <c r="E9" s="20">
+        <v>2.3525518303812909</v>
+      </c>
+      <c r="F9" s="20">
+        <v>6.7075034136015926E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="20">
+        <v>3</v>
+      </c>
+      <c r="B10" s="20">
+        <v>-0.34669506999999999</v>
+      </c>
+      <c r="C10" s="20">
+        <v>1.51773677</v>
+      </c>
+      <c r="D10" s="20">
+        <v>0.95781267000000003</v>
+      </c>
+      <c r="E10" s="20">
+        <v>1.5882835808857616</v>
+      </c>
+      <c r="F10" s="20">
+        <v>9.9350957365919867E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="20">
+        <v>4</v>
+      </c>
+      <c r="B11" s="20">
+        <v>-0.19815698000000001</v>
+      </c>
+      <c r="C11" s="20">
+        <v>-0.58380409</v>
+      </c>
+      <c r="D11" s="20">
+        <v>1.1914404700000001</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0.81897746309610187</v>
+      </c>
+      <c r="F11" s="20">
+        <v>0.19267623523244046</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="20">
+        <v>5</v>
+      </c>
+      <c r="B12" s="20">
+        <v>1.8774217499999999</v>
+      </c>
+      <c r="C12" s="20">
+        <v>-0.75931813999999997</v>
+      </c>
+      <c r="D12" s="20">
+        <v>-1.5503305599999999</v>
+      </c>
+      <c r="E12" s="20">
+        <v>0.98226060952335825</v>
+      </c>
+      <c r="F12" s="20">
+        <v>0.16064727914330501</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="20">
+        <v>6</v>
+      </c>
+      <c r="B13" s="20">
+        <v>-3.4795999999999998E-3</v>
+      </c>
+      <c r="C13" s="20">
+        <v>1.43031814</v>
+      </c>
+      <c r="D13" s="20">
+        <v>-2.1369335899999999</v>
+      </c>
+      <c r="E13" s="20">
+        <v>0.47987274801093366</v>
+      </c>
+      <c r="F13" s="20">
+        <v>0.32883195593756975</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>